--- a/data/irrigation_records.xlsx
+++ b/data/irrigation_records.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="357">
   <si>
     <t>Date</t>
   </si>
@@ -1448,7 +1448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E824"/>
+  <dimension ref="A1:E834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -12977,7 +12977,7 @@
       </c>
     </row>
     <row r="824" spans="1:5">
-      <c r="A824" s="3">
+      <c r="A824" s="2">
         <v>45839</v>
       </c>
       <c r="B824" t="s">
@@ -12987,6 +12987,146 @@
         <v>80</v>
       </c>
       <c r="E824" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="825" spans="1:5">
+      <c r="A825" s="2">
+        <v>45831</v>
+      </c>
+      <c r="B825" t="s">
+        <v>325</v>
+      </c>
+      <c r="C825">
+        <v>80</v>
+      </c>
+      <c r="E825" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="826" spans="1:5">
+      <c r="A826" s="2">
+        <v>45820</v>
+      </c>
+      <c r="B826" t="s">
+        <v>332</v>
+      </c>
+      <c r="C826">
+        <v>80</v>
+      </c>
+      <c r="E826" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="827" spans="1:5">
+      <c r="A827" s="2">
+        <v>45840</v>
+      </c>
+      <c r="B827" t="s">
+        <v>332</v>
+      </c>
+      <c r="C827">
+        <v>80</v>
+      </c>
+      <c r="E827" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="828" spans="1:5">
+      <c r="A828" s="2">
+        <v>45826</v>
+      </c>
+      <c r="B828" t="s">
+        <v>341</v>
+      </c>
+      <c r="C828">
+        <v>80</v>
+      </c>
+      <c r="E828" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="829" spans="1:5">
+      <c r="A829" s="2">
+        <v>45811</v>
+      </c>
+      <c r="B829" t="s">
+        <v>330</v>
+      </c>
+      <c r="C829">
+        <v>80</v>
+      </c>
+      <c r="E829" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="830" spans="1:5">
+      <c r="A830" s="2">
+        <v>45830</v>
+      </c>
+      <c r="B830" t="s">
+        <v>330</v>
+      </c>
+      <c r="C830">
+        <v>80</v>
+      </c>
+      <c r="E830" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="831" spans="1:5">
+      <c r="A831" s="2">
+        <v>45811</v>
+      </c>
+      <c r="B831" t="s">
+        <v>314</v>
+      </c>
+      <c r="C831">
+        <v>80</v>
+      </c>
+      <c r="E831" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="832" spans="1:5">
+      <c r="A832" s="2">
+        <v>45835</v>
+      </c>
+      <c r="B832" t="s">
+        <v>314</v>
+      </c>
+      <c r="C832">
+        <v>80</v>
+      </c>
+      <c r="E832" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="833" spans="1:5">
+      <c r="A833" s="2">
+        <v>45839</v>
+      </c>
+      <c r="B833" t="s">
+        <v>321</v>
+      </c>
+      <c r="C833">
+        <v>80</v>
+      </c>
+      <c r="E833" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="834" spans="1:5">
+      <c r="A834" s="3">
+        <v>45836</v>
+      </c>
+      <c r="B834" t="s">
+        <v>343</v>
+      </c>
+      <c r="C834">
+        <v>80</v>
+      </c>
+      <c r="E834" t="s">
         <v>356</v>
       </c>
     </row>

--- a/data/irrigation_records.xlsx
+++ b/data/irrigation_records.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="358">
   <si>
     <t>Date</t>
   </si>
@@ -1085,17 +1090,20 @@
   </si>
   <si>
     <t>2025/26</t>
+  </si>
+  <si>
+    <t>DG27004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1160,6 +1168,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1206,7 +1222,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1238,9 +1254,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1272,6 +1289,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1447,11 +1465,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E834"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E835"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1468,7 +1489,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1482,7 +1503,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1496,7 +1517,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1510,7 +1531,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1524,7 +1545,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1538,7 +1559,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1552,7 +1573,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1566,7 +1587,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1580,7 +1601,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1594,7 +1615,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1608,7 +1629,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1622,7 +1643,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1636,7 +1657,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1650,7 +1671,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1664,7 +1685,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1678,7 +1699,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1692,7 +1713,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1706,7 +1727,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1720,7 +1741,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1734,7 +1755,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1748,7 +1769,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1762,7 +1783,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1776,7 +1797,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1790,7 +1811,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1804,7 +1825,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1818,7 +1839,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1832,7 +1853,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1846,7 +1867,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1860,7 +1881,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1874,7 +1895,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1888,7 +1909,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1902,7 +1923,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -1916,7 +1937,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -1930,7 +1951,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1944,7 +1965,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -1958,7 +1979,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1972,7 +1993,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1986,7 +2007,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -2000,7 +2021,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -2014,7 +2035,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>24</v>
       </c>
@@ -2028,7 +2049,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -2042,7 +2063,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -2056,7 +2077,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -2070,7 +2091,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -2084,7 +2105,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>28</v>
       </c>
@@ -2098,7 +2119,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -2112,7 +2133,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -2126,7 +2147,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -2140,7 +2161,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -2154,7 +2175,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>22</v>
       </c>
@@ -2168,7 +2189,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -2182,7 +2203,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -2196,7 +2217,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>51</v>
       </c>
@@ -2210,7 +2231,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>52</v>
       </c>
@@ -2224,7 +2245,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>12</v>
       </c>
@@ -2238,7 +2259,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -2252,7 +2273,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>54</v>
       </c>
@@ -2266,7 +2287,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>55</v>
       </c>
@@ -2280,7 +2301,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>56</v>
       </c>
@@ -2294,7 +2315,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>57</v>
       </c>
@@ -2308,7 +2329,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>58</v>
       </c>
@@ -2322,7 +2343,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>59</v>
       </c>
@@ -2336,7 +2357,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>60</v>
       </c>
@@ -2350,7 +2371,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>61</v>
       </c>
@@ -2364,7 +2385,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>62</v>
       </c>
@@ -2378,7 +2399,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -2392,7 +2413,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -2406,7 +2427,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>64</v>
       </c>
@@ -2420,7 +2441,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>65</v>
       </c>
@@ -2434,7 +2455,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>66</v>
       </c>
@@ -2448,7 +2469,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>66</v>
       </c>
@@ -2462,7 +2483,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>67</v>
       </c>
@@ -2476,7 +2497,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -2490,7 +2511,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -2504,7 +2525,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>68</v>
       </c>
@@ -2518,7 +2539,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>69</v>
       </c>
@@ -2532,7 +2553,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -2546,7 +2567,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>20</v>
       </c>
@@ -2560,7 +2581,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>70</v>
       </c>
@@ -2574,7 +2595,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>22</v>
       </c>
@@ -2588,7 +2609,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -2602,7 +2623,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>22</v>
       </c>
@@ -2616,7 +2637,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>71</v>
       </c>
@@ -2630,7 +2651,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>22</v>
       </c>
@@ -2644,7 +2665,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>72</v>
       </c>
@@ -2658,7 +2679,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -2672,7 +2693,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>73</v>
       </c>
@@ -2686,7 +2707,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>51</v>
       </c>
@@ -2700,7 +2721,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>13</v>
       </c>
@@ -2714,7 +2735,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>26</v>
       </c>
@@ -2728,7 +2749,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>74</v>
       </c>
@@ -2742,7 +2763,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>75</v>
       </c>
@@ -2756,7 +2777,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>76</v>
       </c>
@@ -2770,7 +2791,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>76</v>
       </c>
@@ -2784,7 +2805,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2798,7 +2819,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>78</v>
       </c>
@@ -2812,7 +2833,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>79</v>
       </c>
@@ -2826,7 +2847,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>80</v>
       </c>
@@ -2840,7 +2861,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -2854,7 +2875,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>77</v>
       </c>
@@ -2868,7 +2889,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>15</v>
       </c>
@@ -2882,7 +2903,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>81</v>
       </c>
@@ -2896,7 +2917,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>66</v>
       </c>
@@ -2910,7 +2931,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>82</v>
       </c>
@@ -2924,7 +2945,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>83</v>
       </c>
@@ -2938,7 +2959,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -2952,7 +2973,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>47</v>
       </c>
@@ -2966,7 +2987,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>84</v>
       </c>
@@ -2980,7 +3001,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>20</v>
       </c>
@@ -2994,7 +3015,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>22</v>
       </c>
@@ -3008,7 +3029,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>85</v>
       </c>
@@ -3022,7 +3043,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>86</v>
       </c>
@@ -3036,7 +3057,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>87</v>
       </c>
@@ -3050,7 +3071,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>72</v>
       </c>
@@ -3064,7 +3085,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>23</v>
       </c>
@@ -3078,7 +3099,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>88</v>
       </c>
@@ -3092,7 +3113,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -3106,7 +3127,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>23</v>
       </c>
@@ -3120,7 +3141,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>89</v>
       </c>
@@ -3134,7 +3155,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>90</v>
       </c>
@@ -3148,7 +3169,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>91</v>
       </c>
@@ -3162,7 +3183,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -3176,7 +3197,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>92</v>
       </c>
@@ -3190,7 +3211,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>45</v>
       </c>
@@ -3204,7 +3225,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>81</v>
       </c>
@@ -3218,7 +3239,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>62</v>
       </c>
@@ -3232,7 +3253,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>93</v>
       </c>
@@ -3246,7 +3267,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>94</v>
       </c>
@@ -3260,7 +3281,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>95</v>
       </c>
@@ -3274,7 +3295,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>96</v>
       </c>
@@ -3288,7 +3309,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>97</v>
       </c>
@@ -3302,7 +3323,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>98</v>
       </c>
@@ -3316,7 +3337,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>95</v>
       </c>
@@ -3330,7 +3351,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>99</v>
       </c>
@@ -3344,7 +3365,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>100</v>
       </c>
@@ -3358,7 +3379,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>96</v>
       </c>
@@ -3372,7 +3393,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>47</v>
       </c>
@@ -3386,7 +3407,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>101</v>
       </c>
@@ -3400,7 +3421,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>102</v>
       </c>
@@ -3414,7 +3435,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>102</v>
       </c>
@@ -3428,7 +3449,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>69</v>
       </c>
@@ -3442,7 +3463,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>87</v>
       </c>
@@ -3456,7 +3477,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>85</v>
       </c>
@@ -3470,7 +3491,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>49</v>
       </c>
@@ -3484,7 +3505,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>103</v>
       </c>
@@ -3498,7 +3519,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>22</v>
       </c>
@@ -3512,7 +3533,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>104</v>
       </c>
@@ -3526,7 +3547,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>23</v>
       </c>
@@ -3540,7 +3561,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>24</v>
       </c>
@@ -3554,7 +3575,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>24</v>
       </c>
@@ -3568,7 +3589,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>23</v>
       </c>
@@ -3582,7 +3603,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>105</v>
       </c>
@@ -3596,7 +3617,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -3610,7 +3631,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>106</v>
       </c>
@@ -3624,7 +3645,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>107</v>
       </c>
@@ -3638,7 +3659,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>108</v>
       </c>
@@ -3652,7 +3673,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>109</v>
       </c>
@@ -3666,7 +3687,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>29</v>
       </c>
@@ -3680,7 +3701,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>82</v>
       </c>
@@ -3694,7 +3715,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>92</v>
       </c>
@@ -3708,7 +3729,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>110</v>
       </c>
@@ -3722,7 +3743,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>109</v>
       </c>
@@ -3736,7 +3757,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>14</v>
       </c>
@@ -3750,7 +3771,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>111</v>
       </c>
@@ -3764,7 +3785,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>82</v>
       </c>
@@ -3778,7 +3799,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>66</v>
       </c>
@@ -3792,7 +3813,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>112</v>
       </c>
@@ -3806,7 +3827,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>99</v>
       </c>
@@ -3820,7 +3841,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>46</v>
       </c>
@@ -3834,7 +3855,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>101</v>
       </c>
@@ -3848,7 +3869,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>113</v>
       </c>
@@ -3862,7 +3883,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>67</v>
       </c>
@@ -3876,7 +3897,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>114</v>
       </c>
@@ -3890,7 +3911,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>47</v>
       </c>
@@ -3904,7 +3925,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>115</v>
       </c>
@@ -3918,7 +3939,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>115</v>
       </c>
@@ -3932,7 +3953,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>116</v>
       </c>
@@ -3946,7 +3967,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>23</v>
       </c>
@@ -3960,7 +3981,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>22</v>
       </c>
@@ -3974,7 +3995,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>22</v>
       </c>
@@ -3988,7 +4009,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>24</v>
       </c>
@@ -4002,7 +4023,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>34</v>
       </c>
@@ -4016,7 +4037,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>24</v>
       </c>
@@ -4030,7 +4051,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>24</v>
       </c>
@@ -4044,7 +4065,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>117</v>
       </c>
@@ -4058,7 +4079,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>118</v>
       </c>
@@ -4072,7 +4093,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>24</v>
       </c>
@@ -4086,7 +4107,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>23</v>
       </c>
@@ -4100,7 +4121,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>37</v>
       </c>
@@ -4114,7 +4135,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>119</v>
       </c>
@@ -4128,7 +4149,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>120</v>
       </c>
@@ -4142,7 +4163,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>121</v>
       </c>
@@ -4156,7 +4177,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>81</v>
       </c>
@@ -4170,7 +4191,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>122</v>
       </c>
@@ -4184,7 +4205,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>15</v>
       </c>
@@ -4198,7 +4219,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>67</v>
       </c>
@@ -4212,7 +4233,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>111</v>
       </c>
@@ -4226,7 +4247,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>65</v>
       </c>
@@ -4240,7 +4261,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>112</v>
       </c>
@@ -4254,7 +4275,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>17</v>
       </c>
@@ -4268,7 +4289,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>123</v>
       </c>
@@ -4282,7 +4303,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>122</v>
       </c>
@@ -4296,7 +4317,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>124</v>
       </c>
@@ -4310,7 +4331,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>17</v>
       </c>
@@ -4324,7 +4345,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>47</v>
       </c>
@@ -4338,7 +4359,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>17</v>
       </c>
@@ -4352,7 +4373,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>125</v>
       </c>
@@ -4366,7 +4387,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>126</v>
       </c>
@@ -4380,7 +4401,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>85</v>
       </c>
@@ -4394,7 +4415,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>20</v>
       </c>
@@ -4408,7 +4429,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>127</v>
       </c>
@@ -4422,7 +4443,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>128</v>
       </c>
@@ -4436,7 +4457,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>24</v>
       </c>
@@ -4450,7 +4471,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>23</v>
       </c>
@@ -4464,7 +4485,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>105</v>
       </c>
@@ -4478,7 +4499,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>90</v>
       </c>
@@ -4492,7 +4513,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>103</v>
       </c>
@@ -4506,7 +4527,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>129</v>
       </c>
@@ -4520,7 +4541,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>130</v>
       </c>
@@ -4534,7 +4555,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>131</v>
       </c>
@@ -4548,7 +4569,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>132</v>
       </c>
@@ -4562,7 +4583,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>133</v>
       </c>
@@ -4576,7 +4597,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>24</v>
       </c>
@@ -4590,7 +4611,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>134</v>
       </c>
@@ -4604,7 +4625,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>135</v>
       </c>
@@ -4618,7 +4639,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>136</v>
       </c>
@@ -4632,7 +4653,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>137</v>
       </c>
@@ -4646,7 +4667,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>138</v>
       </c>
@@ -4660,7 +4681,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>96</v>
       </c>
@@ -4674,7 +4695,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>139</v>
       </c>
@@ -4688,7 +4709,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>29</v>
       </c>
@@ -4702,7 +4723,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>140</v>
       </c>
@@ -4716,7 +4737,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>141</v>
       </c>
@@ -4730,7 +4751,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>84</v>
       </c>
@@ -4744,7 +4765,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>142</v>
       </c>
@@ -4758,7 +4779,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>101</v>
       </c>
@@ -4772,7 +4793,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>123</v>
       </c>
@@ -4786,7 +4807,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>39</v>
       </c>
@@ -4800,7 +4821,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>32</v>
       </c>
@@ -4814,7 +4835,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>143</v>
       </c>
@@ -4828,7 +4849,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>144</v>
       </c>
@@ -4842,7 +4863,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>35</v>
       </c>
@@ -4856,7 +4877,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>22</v>
       </c>
@@ -4870,7 +4891,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>33</v>
       </c>
@@ -4884,7 +4905,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>34</v>
       </c>
@@ -4898,7 +4919,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>126</v>
       </c>
@@ -4912,7 +4933,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>117</v>
       </c>
@@ -4926,7 +4947,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>24</v>
       </c>
@@ -4940,7 +4961,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>23</v>
       </c>
@@ -4954,7 +4975,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>145</v>
       </c>
@@ -4968,7 +4989,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>24</v>
       </c>
@@ -4982,7 +5003,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>146</v>
       </c>
@@ -4996,7 +5017,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>37</v>
       </c>
@@ -5010,7 +5031,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>147</v>
       </c>
@@ -5024,7 +5045,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>136</v>
       </c>
@@ -5038,7 +5059,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>89</v>
       </c>
@@ -5052,7 +5073,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>90</v>
       </c>
@@ -5066,7 +5087,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>148</v>
       </c>
@@ -5080,7 +5101,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>119</v>
       </c>
@@ -5094,7 +5115,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>149</v>
       </c>
@@ -5108,7 +5129,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>38</v>
       </c>
@@ -5122,7 +5143,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>17</v>
       </c>
@@ -5136,7 +5157,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>110</v>
       </c>
@@ -5150,7 +5171,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>20</v>
       </c>
@@ -5164,7 +5185,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>150</v>
       </c>
@@ -5178,7 +5199,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>151</v>
       </c>
@@ -5192,7 +5213,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>122</v>
       </c>
@@ -5206,7 +5227,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>152</v>
       </c>
@@ -5220,7 +5241,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>19</v>
       </c>
@@ -5234,7 +5255,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>38</v>
       </c>
@@ -5248,7 +5269,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>47</v>
       </c>
@@ -5262,7 +5283,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>20</v>
       </c>
@@ -5276,7 +5297,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>20</v>
       </c>
@@ -5290,7 +5311,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>139</v>
       </c>
@@ -5304,7 +5325,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>41</v>
       </c>
@@ -5318,7 +5339,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>24</v>
       </c>
@@ -5332,7 +5353,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>23</v>
       </c>
@@ -5346,7 +5367,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>23</v>
       </c>
@@ -5360,7 +5381,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>23</v>
       </c>
@@ -5374,7 +5395,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>23</v>
       </c>
@@ -5388,7 +5409,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>146</v>
       </c>
@@ -5402,7 +5423,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>37</v>
       </c>
@@ -5416,7 +5437,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>24</v>
       </c>
@@ -5430,7 +5451,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>106</v>
       </c>
@@ -5444,7 +5465,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>37</v>
       </c>
@@ -5458,7 +5479,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>153</v>
       </c>
@@ -5472,7 +5493,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>154</v>
       </c>
@@ -5486,7 +5507,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>155</v>
       </c>
@@ -5500,7 +5521,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>156</v>
       </c>
@@ -5514,7 +5535,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>157</v>
       </c>
@@ -5528,7 +5549,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>158</v>
       </c>
@@ -5542,7 +5563,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>159</v>
       </c>
@@ -5556,7 +5577,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>160</v>
       </c>
@@ -5570,7 +5591,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>68</v>
       </c>
@@ -5584,7 +5605,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>68</v>
       </c>
@@ -5598,7 +5619,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>67</v>
       </c>
@@ -5612,7 +5633,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>22</v>
       </c>
@@ -5626,7 +5647,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>67</v>
       </c>
@@ -5640,7 +5661,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>161</v>
       </c>
@@ -5654,7 +5675,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>151</v>
       </c>
@@ -5668,7 +5689,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>41</v>
       </c>
@@ -5682,7 +5703,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>20</v>
       </c>
@@ -5696,7 +5717,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>125</v>
       </c>
@@ -5710,7 +5731,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>32</v>
       </c>
@@ -5724,7 +5745,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>49</v>
       </c>
@@ -5738,7 +5759,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>22</v>
       </c>
@@ -5752,7 +5773,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>21</v>
       </c>
@@ -5766,7 +5787,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>126</v>
       </c>
@@ -5780,7 +5801,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>162</v>
       </c>
@@ -5794,7 +5815,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>24</v>
       </c>
@@ -5808,7 +5829,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>24</v>
       </c>
@@ -5822,7 +5843,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>24</v>
       </c>
@@ -5836,7 +5857,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>24</v>
       </c>
@@ -5850,7 +5871,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>132</v>
       </c>
@@ -5864,7 +5885,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>90</v>
       </c>
@@ -5878,7 +5899,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>148</v>
       </c>
@@ -5892,7 +5913,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>163</v>
       </c>
@@ -5906,7 +5927,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>145</v>
       </c>
@@ -5920,7 +5941,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>164</v>
       </c>
@@ -5934,7 +5955,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>165</v>
       </c>
@@ -5948,7 +5969,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>166</v>
       </c>
@@ -5962,7 +5983,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>167</v>
       </c>
@@ -5976,7 +5997,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>168</v>
       </c>
@@ -5990,7 +6011,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>169</v>
       </c>
@@ -6004,7 +6025,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>20</v>
       </c>
@@ -6018,7 +6039,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>48</v>
       </c>
@@ -6032,7 +6053,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>20</v>
       </c>
@@ -6046,7 +6067,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>22</v>
       </c>
@@ -6060,7 +6081,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>47</v>
       </c>
@@ -6074,7 +6095,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>39</v>
       </c>
@@ -6088,7 +6109,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>123</v>
       </c>
@@ -6102,7 +6123,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>72</v>
       </c>
@@ -6116,7 +6137,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>127</v>
       </c>
@@ -6130,7 +6151,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>39</v>
       </c>
@@ -6144,7 +6165,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>114</v>
       </c>
@@ -6158,7 +6179,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>22</v>
       </c>
@@ -6172,7 +6193,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>23</v>
       </c>
@@ -6186,7 +6207,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>105</v>
       </c>
@@ -6200,7 +6221,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>23</v>
       </c>
@@ -6214,7 +6235,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>170</v>
       </c>
@@ -6228,7 +6249,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>73</v>
       </c>
@@ -6242,7 +6263,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>171</v>
       </c>
@@ -6256,7 +6277,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>172</v>
       </c>
@@ -6270,7 +6291,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>36</v>
       </c>
@@ -6284,7 +6305,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>173</v>
       </c>
@@ -6298,7 +6319,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>174</v>
       </c>
@@ -6312,7 +6333,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>107</v>
       </c>
@@ -6326,7 +6347,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>120</v>
       </c>
@@ -6340,7 +6361,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>175</v>
       </c>
@@ -6354,7 +6375,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>176</v>
       </c>
@@ -6368,7 +6389,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>177</v>
       </c>
@@ -6382,7 +6403,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>178</v>
       </c>
@@ -6396,7 +6417,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>179</v>
       </c>
@@ -6410,7 +6431,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>180</v>
       </c>
@@ -6424,7 +6445,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>22</v>
       </c>
@@ -6438,7 +6459,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>22</v>
       </c>
@@ -6452,7 +6473,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>21</v>
       </c>
@@ -6466,7 +6487,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>23</v>
       </c>
@@ -6480,7 +6501,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>139</v>
       </c>
@@ -6494,7 +6515,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>128</v>
       </c>
@@ -6508,7 +6529,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>38</v>
       </c>
@@ -6522,7 +6543,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>24</v>
       </c>
@@ -6536,7 +6557,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>181</v>
       </c>
@@ -6550,7 +6571,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>21</v>
       </c>
@@ -6564,7 +6585,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>22</v>
       </c>
@@ -6578,7 +6599,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>88</v>
       </c>
@@ -6592,7 +6613,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>24</v>
       </c>
@@ -6606,7 +6627,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>163</v>
       </c>
@@ -6620,7 +6641,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>182</v>
       </c>
@@ -6634,7 +6655,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>131</v>
       </c>
@@ -6648,7 +6669,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>118</v>
       </c>
@@ -6662,7 +6683,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>164</v>
       </c>
@@ -6676,7 +6697,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>107</v>
       </c>
@@ -6690,7 +6711,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>135</v>
       </c>
@@ -6704,7 +6725,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>183</v>
       </c>
@@ -6718,7 +6739,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>184</v>
       </c>
@@ -6732,7 +6753,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>156</v>
       </c>
@@ -6746,7 +6767,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>185</v>
       </c>
@@ -6760,7 +6781,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>23</v>
       </c>
@@ -6774,7 +6795,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>23</v>
       </c>
@@ -6788,7 +6809,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>41</v>
       </c>
@@ -6802,7 +6823,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>24</v>
       </c>
@@ -6816,7 +6837,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>71</v>
       </c>
@@ -6830,7 +6851,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>87</v>
       </c>
@@ -6844,7 +6865,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>47</v>
       </c>
@@ -6858,7 +6879,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>186</v>
       </c>
@@ -6872,7 +6893,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>42</v>
       </c>
@@ -6886,7 +6907,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>70</v>
       </c>
@@ -6900,7 +6921,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>35</v>
       </c>
@@ -6914,7 +6935,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>187</v>
       </c>
@@ -6928,7 +6949,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>117</v>
       </c>
@@ -6942,7 +6963,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>24</v>
       </c>
@@ -6956,7 +6977,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>188</v>
       </c>
@@ -6970,7 +6991,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>189</v>
       </c>
@@ -6984,7 +7005,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>131</v>
       </c>
@@ -6998,7 +7019,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>190</v>
       </c>
@@ -7012,7 +7033,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>191</v>
       </c>
@@ -7026,7 +7047,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>192</v>
       </c>
@@ -7040,7 +7061,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>190</v>
       </c>
@@ -7054,7 +7075,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>193</v>
       </c>
@@ -7068,7 +7089,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>194</v>
       </c>
@@ -7082,7 +7103,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>195</v>
       </c>
@@ -7096,7 +7117,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>196</v>
       </c>
@@ -7110,7 +7131,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>50</v>
       </c>
@@ -7124,7 +7145,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>50</v>
       </c>
@@ -7138,7 +7159,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>22</v>
       </c>
@@ -7152,7 +7173,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>126</v>
       </c>
@@ -7166,7 +7187,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>103</v>
       </c>
@@ -7180,7 +7201,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>39</v>
       </c>
@@ -7194,7 +7215,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>23</v>
       </c>
@@ -7208,7 +7229,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>34</v>
       </c>
@@ -7222,7 +7243,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>24</v>
       </c>
@@ -7236,7 +7257,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>197</v>
       </c>
@@ -7250,7 +7271,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>146</v>
       </c>
@@ -7264,7 +7285,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>172</v>
       </c>
@@ -7278,7 +7299,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>156</v>
       </c>
@@ -7292,7 +7313,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>198</v>
       </c>
@@ -7306,7 +7327,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>173</v>
       </c>
@@ -7320,7 +7341,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>199</v>
       </c>
@@ -7334,7 +7355,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>200</v>
       </c>
@@ -7348,7 +7369,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>132</v>
       </c>
@@ -7362,7 +7383,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>201</v>
       </c>
@@ -7376,7 +7397,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>202</v>
       </c>
@@ -7390,7 +7411,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>171</v>
       </c>
@@ -7404,7 +7425,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>34</v>
       </c>
@@ -7418,7 +7439,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>23</v>
       </c>
@@ -7432,7 +7453,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="428" spans="1:5">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>24</v>
       </c>
@@ -7446,7 +7467,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="429" spans="1:5">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>32</v>
       </c>
@@ -7460,7 +7481,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="430" spans="1:5">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>24</v>
       </c>
@@ -7474,7 +7495,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="431" spans="1:5">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>104</v>
       </c>
@@ -7488,7 +7509,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="432" spans="1:5">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>36</v>
       </c>
@@ -7502,7 +7523,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="433" spans="1:5">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>203</v>
       </c>
@@ -7516,7 +7537,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="434" spans="1:5">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>118</v>
       </c>
@@ -7530,7 +7551,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="435" spans="1:5">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>119</v>
       </c>
@@ -7544,7 +7565,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="436" spans="1:5">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>136</v>
       </c>
@@ -7558,7 +7579,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="437" spans="1:5">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>201</v>
       </c>
@@ -7572,7 +7593,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="438" spans="1:5">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>155</v>
       </c>
@@ -7586,7 +7607,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="439" spans="1:5">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>106</v>
       </c>
@@ -7600,7 +7621,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="440" spans="1:5">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>204</v>
       </c>
@@ -7614,7 +7635,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="441" spans="1:5">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>205</v>
       </c>
@@ -7628,7 +7649,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="442" spans="1:5">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>23</v>
       </c>
@@ -7642,7 +7663,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="443" spans="1:5">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>24</v>
       </c>
@@ -7656,7 +7677,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="444" spans="1:5">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>37</v>
       </c>
@@ -7670,7 +7691,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="445" spans="1:5">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>40</v>
       </c>
@@ -7684,7 +7705,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="446" spans="1:5">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>206</v>
       </c>
@@ -7698,7 +7719,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="447" spans="1:5">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>24</v>
       </c>
@@ -7712,7 +7733,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="448" spans="1:5">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>37</v>
       </c>
@@ -7726,7 +7747,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="449" spans="1:5">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>175</v>
       </c>
@@ -7740,7 +7761,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="450" spans="1:5">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>196</v>
       </c>
@@ -7754,7 +7775,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="451" spans="1:5">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>207</v>
       </c>
@@ -7768,7 +7789,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="452" spans="1:5">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>208</v>
       </c>
@@ -7782,7 +7803,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="453" spans="1:5">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>209</v>
       </c>
@@ -7796,7 +7817,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="454" spans="1:5">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>210</v>
       </c>
@@ -7810,7 +7831,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="455" spans="1:5">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>211</v>
       </c>
@@ -7824,7 +7845,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="456" spans="1:5">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>24</v>
       </c>
@@ -7838,7 +7859,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="457" spans="1:5">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>36</v>
       </c>
@@ -7852,7 +7873,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="458" spans="1:5">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>114</v>
       </c>
@@ -7866,7 +7887,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="459" spans="1:5">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>89</v>
       </c>
@@ -7880,7 +7901,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="460" spans="1:5">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>212</v>
       </c>
@@ -7894,7 +7915,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="461" spans="1:5">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>213</v>
       </c>
@@ -7908,7 +7929,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="462" spans="1:5">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>214</v>
       </c>
@@ -7922,7 +7943,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="463" spans="1:5">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>192</v>
       </c>
@@ -7936,7 +7957,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="464" spans="1:5">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>215</v>
       </c>
@@ -7950,7 +7971,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="465" spans="1:5">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>200</v>
       </c>
@@ -7964,7 +7985,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="466" spans="1:5">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>202</v>
       </c>
@@ -7978,7 +7999,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="467" spans="1:5">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="2">
         <v>45611</v>
       </c>
@@ -7992,7 +8013,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="468" spans="1:5">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>216</v>
       </c>
@@ -8006,7 +8027,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="469" spans="1:5">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>217</v>
       </c>
@@ -8020,7 +8041,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="470" spans="1:5">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>199</v>
       </c>
@@ -8034,7 +8055,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="471" spans="1:5">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>218</v>
       </c>
@@ -8048,7 +8069,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="472" spans="1:5">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>219</v>
       </c>
@@ -8062,7 +8083,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="473" spans="1:5">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>205</v>
       </c>
@@ -8076,7 +8097,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="474" spans="1:5">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>181</v>
       </c>
@@ -8090,7 +8111,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="475" spans="1:5">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>178</v>
       </c>
@@ -8104,7 +8125,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="476" spans="1:5">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>220</v>
       </c>
@@ -8118,7 +8139,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="477" spans="1:5">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>221</v>
       </c>
@@ -8132,7 +8153,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="478" spans="1:5">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>222</v>
       </c>
@@ -8146,7 +8167,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="479" spans="1:5">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>223</v>
       </c>
@@ -8160,7 +8181,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="480" spans="1:5">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>126</v>
       </c>
@@ -8174,7 +8195,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="481" spans="1:5">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>224</v>
       </c>
@@ -8188,7 +8209,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="482" spans="1:5">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>149</v>
       </c>
@@ -8202,7 +8223,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="483" spans="1:5">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>225</v>
       </c>
@@ -8216,7 +8237,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="484" spans="1:5">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>160</v>
       </c>
@@ -8230,7 +8251,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="485" spans="1:5">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>177</v>
       </c>
@@ -8244,7 +8265,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="486" spans="1:5">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>103</v>
       </c>
@@ -8258,7 +8279,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="487" spans="1:5">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>226</v>
       </c>
@@ -8272,7 +8293,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="488" spans="1:5">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>89</v>
       </c>
@@ -8286,7 +8307,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="489" spans="1:5">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>186</v>
       </c>
@@ -8300,7 +8321,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="490" spans="1:5">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>153</v>
       </c>
@@ -8314,7 +8335,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="491" spans="1:5">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>227</v>
       </c>
@@ -8328,7 +8349,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="492" spans="1:5">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>228</v>
       </c>
@@ -8342,7 +8363,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="493" spans="1:5">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>229</v>
       </c>
@@ -8356,7 +8377,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="494" spans="1:5">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>230</v>
       </c>
@@ -8370,7 +8391,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="495" spans="1:5">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>231</v>
       </c>
@@ -8384,7 +8405,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="496" spans="1:5">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>167</v>
       </c>
@@ -8398,7 +8419,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="497" spans="1:5">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>232</v>
       </c>
@@ -8412,7 +8433,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="498" spans="1:5">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>148</v>
       </c>
@@ -8426,7 +8447,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="499" spans="1:5">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>158</v>
       </c>
@@ -8440,7 +8461,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="500" spans="1:5">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>233</v>
       </c>
@@ -8454,7 +8475,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="501" spans="1:5">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>189</v>
       </c>
@@ -8468,7 +8489,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="502" spans="1:5">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>233</v>
       </c>
@@ -8482,7 +8503,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="503" spans="1:5">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>166</v>
       </c>
@@ -8496,7 +8517,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="504" spans="1:5">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>233</v>
       </c>
@@ -8510,7 +8531,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="505" spans="1:5">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>189</v>
       </c>
@@ -8524,7 +8545,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="506" spans="1:5">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>233</v>
       </c>
@@ -8538,7 +8559,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="507" spans="1:5">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>166</v>
       </c>
@@ -8552,7 +8573,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="508" spans="1:5">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>234</v>
       </c>
@@ -8566,7 +8587,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="509" spans="1:5">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>204</v>
       </c>
@@ -8580,7 +8601,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="510" spans="1:5">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>149</v>
       </c>
@@ -8594,7 +8615,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="511" spans="1:5">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>176</v>
       </c>
@@ -8608,7 +8629,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="512" spans="1:5">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>192</v>
       </c>
@@ -8622,7 +8643,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="513" spans="1:5">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>199</v>
       </c>
@@ -8636,7 +8657,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="514" spans="1:5">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>235</v>
       </c>
@@ -8650,7 +8671,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="515" spans="1:5">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>236</v>
       </c>
@@ -8664,7 +8685,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="516" spans="1:5">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>237</v>
       </c>
@@ -8678,7 +8699,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="517" spans="1:5">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>165</v>
       </c>
@@ -8692,7 +8713,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="518" spans="1:5">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>237</v>
       </c>
@@ -8706,7 +8727,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="519" spans="1:5">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>238</v>
       </c>
@@ -8720,7 +8741,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="520" spans="1:5">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>239</v>
       </c>
@@ -8734,7 +8755,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="521" spans="1:5">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>240</v>
       </c>
@@ -8748,7 +8769,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="522" spans="1:5">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>241</v>
       </c>
@@ -8762,7 +8783,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="523" spans="1:5">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>242</v>
       </c>
@@ -8776,7 +8797,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="524" spans="1:5">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>243</v>
       </c>
@@ -8790,7 +8811,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="525" spans="1:5">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>243</v>
       </c>
@@ -8804,7 +8825,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="526" spans="1:5">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>244</v>
       </c>
@@ -8818,7 +8839,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="527" spans="1:5">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>243</v>
       </c>
@@ -8832,7 +8853,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="528" spans="1:5">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>243</v>
       </c>
@@ -8846,7 +8867,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="529" spans="1:5">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>245</v>
       </c>
@@ -8860,7 +8881,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="530" spans="1:5">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>246</v>
       </c>
@@ -8874,7 +8895,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="531" spans="1:5">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>228</v>
       </c>
@@ -8888,7 +8909,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="532" spans="1:5">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>232</v>
       </c>
@@ -8902,7 +8923,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="533" spans="1:5">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>247</v>
       </c>
@@ -8916,7 +8937,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="534" spans="1:5">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>248</v>
       </c>
@@ -8930,7 +8951,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="535" spans="1:5">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>230</v>
       </c>
@@ -8944,7 +8965,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="536" spans="1:5">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>247</v>
       </c>
@@ -8958,7 +8979,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="537" spans="1:5">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>145</v>
       </c>
@@ -8972,7 +8993,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="538" spans="1:5">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>178</v>
       </c>
@@ -8986,7 +9007,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="539" spans="1:5">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>249</v>
       </c>
@@ -9000,7 +9021,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="540" spans="1:5">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>250</v>
       </c>
@@ -9014,7 +9035,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="541" spans="1:5">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>250</v>
       </c>
@@ -9028,7 +9049,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="542" spans="1:5">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>107</v>
       </c>
@@ -9042,7 +9063,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="543" spans="1:5">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>251</v>
       </c>
@@ -9056,7 +9077,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="544" spans="1:5">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>147</v>
       </c>
@@ -9070,7 +9091,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="545" spans="1:5">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>106</v>
       </c>
@@ -9084,7 +9105,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="546" spans="1:5">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>106</v>
       </c>
@@ -9098,7 +9119,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="547" spans="1:5">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>252</v>
       </c>
@@ -9112,7 +9133,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>219</v>
       </c>
@@ -9126,7 +9147,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="549" spans="1:5">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>160</v>
       </c>
@@ -9140,7 +9161,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="550" spans="1:5">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>222</v>
       </c>
@@ -9154,7 +9175,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="551" spans="1:5">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>235</v>
       </c>
@@ -9168,7 +9189,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="552" spans="1:5">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>169</v>
       </c>
@@ -9182,7 +9203,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>253</v>
       </c>
@@ -9196,7 +9217,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="554" spans="1:5">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>237</v>
       </c>
@@ -9210,7 +9231,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="555" spans="1:5">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>237</v>
       </c>
@@ -9224,7 +9245,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="556" spans="1:5">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>254</v>
       </c>
@@ -9238,7 +9259,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="557" spans="1:5">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>255</v>
       </c>
@@ -9252,7 +9273,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="558" spans="1:5">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>225</v>
       </c>
@@ -9266,7 +9287,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="559" spans="1:5">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>254</v>
       </c>
@@ -9280,7 +9301,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="560" spans="1:5">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>241</v>
       </c>
@@ -9294,7 +9315,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="561" spans="1:5">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>256</v>
       </c>
@@ -9308,7 +9329,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="562" spans="1:5">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>245</v>
       </c>
@@ -9322,7 +9343,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="563" spans="1:5">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>257</v>
       </c>
@@ -9336,7 +9357,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="564" spans="1:5">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>245</v>
       </c>
@@ -9350,7 +9371,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="565" spans="1:5">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>245</v>
       </c>
@@ -9364,7 +9385,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="566" spans="1:5">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>245</v>
       </c>
@@ -9378,7 +9399,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="567" spans="1:5">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>245</v>
       </c>
@@ -9392,7 +9413,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="568" spans="1:5">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>245</v>
       </c>
@@ -9406,7 +9427,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="569" spans="1:5">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>258</v>
       </c>
@@ -9420,7 +9441,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="570" spans="1:5">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>259</v>
       </c>
@@ -9434,7 +9455,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="571" spans="1:5">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>191</v>
       </c>
@@ -9448,7 +9469,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="572" spans="1:5">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>175</v>
       </c>
@@ -9462,7 +9483,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="573" spans="1:5">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>203</v>
       </c>
@@ -9476,7 +9497,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="574" spans="1:5">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>182</v>
       </c>
@@ -9490,7 +9511,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="575" spans="1:5">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>260</v>
       </c>
@@ -9504,7 +9525,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="576" spans="1:5">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>131</v>
       </c>
@@ -9518,7 +9539,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="577" spans="1:5">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>189</v>
       </c>
@@ -9532,7 +9553,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="578" spans="1:5">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>107</v>
       </c>
@@ -9546,7 +9567,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="579" spans="1:5">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>166</v>
       </c>
@@ -9560,7 +9581,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="580" spans="1:5">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>195</v>
       </c>
@@ -9574,7 +9595,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="581" spans="1:5">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>108</v>
       </c>
@@ -9588,7 +9609,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="582" spans="1:5">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>173</v>
       </c>
@@ -9602,7 +9623,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="583" spans="1:5">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>201</v>
       </c>
@@ -9616,7 +9637,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="584" spans="1:5">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>220</v>
       </c>
@@ -9630,7 +9651,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="585" spans="1:5">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>159</v>
       </c>
@@ -9644,7 +9665,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="586" spans="1:5">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>261</v>
       </c>
@@ -9658,7 +9679,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="587" spans="1:5">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>262</v>
       </c>
@@ -9672,7 +9693,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="588" spans="1:5">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>263</v>
       </c>
@@ -9686,7 +9707,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="589" spans="1:5">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>264</v>
       </c>
@@ -9700,7 +9721,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="590" spans="1:5">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>218</v>
       </c>
@@ -9714,7 +9735,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="591" spans="1:5">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>240</v>
       </c>
@@ -9728,7 +9749,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="592" spans="1:5">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>225</v>
       </c>
@@ -9742,7 +9763,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="593" spans="1:5">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>221</v>
       </c>
@@ -9756,7 +9777,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="594" spans="1:5">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>265</v>
       </c>
@@ -9770,7 +9791,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="595" spans="1:5">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>240</v>
       </c>
@@ -9784,7 +9805,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="596" spans="1:5">
+    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>226</v>
       </c>
@@ -9798,7 +9819,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="597" spans="1:5">
+    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>266</v>
       </c>
@@ -9812,7 +9833,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="598" spans="1:5">
+    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>267</v>
       </c>
@@ -9826,7 +9847,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="599" spans="1:5">
+    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>268</v>
       </c>
@@ -9840,7 +9861,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="600" spans="1:5">
+    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>245</v>
       </c>
@@ -9854,7 +9875,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="601" spans="1:5">
+    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>245</v>
       </c>
@@ -9868,7 +9889,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="602" spans="1:5">
+    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>156</v>
       </c>
@@ -9882,7 +9903,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="603" spans="1:5">
+    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>121</v>
       </c>
@@ -9896,7 +9917,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="604" spans="1:5">
+    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>198</v>
       </c>
@@ -9910,7 +9931,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="605" spans="1:5">
+    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>251</v>
       </c>
@@ -9924,7 +9945,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="606" spans="1:5">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>260</v>
       </c>
@@ -9938,7 +9959,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="607" spans="1:5">
+    <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>107</v>
       </c>
@@ -9952,7 +9973,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="608" spans="1:5">
+    <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>147</v>
       </c>
@@ -9966,7 +9987,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="609" spans="1:5">
+    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>190</v>
       </c>
@@ -9980,7 +10001,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="610" spans="1:5">
+    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>166</v>
       </c>
@@ -9994,7 +10015,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="611" spans="1:5">
+    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>149</v>
       </c>
@@ -10008,7 +10029,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="612" spans="1:5">
+    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>269</v>
       </c>
@@ -10022,7 +10043,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="613" spans="1:5">
+    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>269</v>
       </c>
@@ -10036,7 +10057,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="614" spans="1:5">
+    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>220</v>
       </c>
@@ -10050,7 +10071,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="615" spans="1:5">
+    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>270</v>
       </c>
@@ -10064,7 +10085,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="616" spans="1:5">
+    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>207</v>
       </c>
@@ -10078,7 +10099,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="617" spans="1:5">
+    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>271</v>
       </c>
@@ -10092,7 +10113,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="618" spans="1:5">
+    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>272</v>
       </c>
@@ -10106,7 +10127,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="619" spans="1:5">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>264</v>
       </c>
@@ -10120,7 +10141,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="620" spans="1:5">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>273</v>
       </c>
@@ -10134,7 +10155,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="621" spans="1:5">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>274</v>
       </c>
@@ -10148,7 +10169,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="622" spans="1:5">
+    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>275</v>
       </c>
@@ -10162,7 +10183,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="623" spans="1:5">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>276</v>
       </c>
@@ -10176,7 +10197,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="624" spans="1:5">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>277</v>
       </c>
@@ -10190,7 +10211,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="625" spans="1:5">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>278</v>
       </c>
@@ -10204,7 +10225,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="626" spans="1:5">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>245</v>
       </c>
@@ -10218,7 +10239,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="627" spans="1:5">
+    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>275</v>
       </c>
@@ -10232,7 +10253,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="628" spans="1:5">
+    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>279</v>
       </c>
@@ -10246,7 +10267,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="629" spans="1:5">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>280</v>
       </c>
@@ -10260,7 +10281,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="630" spans="1:5">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>276</v>
       </c>
@@ -10274,7 +10295,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="631" spans="1:5">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>245</v>
       </c>
@@ -10288,7 +10309,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="632" spans="1:5">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>121</v>
       </c>
@@ -10302,7 +10323,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="633" spans="1:5">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>281</v>
       </c>
@@ -10316,7 +10337,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="634" spans="1:5">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>154</v>
       </c>
@@ -10330,7 +10351,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="635" spans="1:5">
+    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>166</v>
       </c>
@@ -10344,7 +10365,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="636" spans="1:5">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>250</v>
       </c>
@@ -10358,7 +10379,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="637" spans="1:5">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>217</v>
       </c>
@@ -10372,7 +10393,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="638" spans="1:5">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>269</v>
       </c>
@@ -10386,7 +10407,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="639" spans="1:5">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>136</v>
       </c>
@@ -10400,7 +10421,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="640" spans="1:5">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>252</v>
       </c>
@@ -10414,7 +10435,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="641" spans="1:5">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>202</v>
       </c>
@@ -10428,7 +10449,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="642" spans="1:5">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>282</v>
       </c>
@@ -10442,7 +10463,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="643" spans="1:5">
+    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>207</v>
       </c>
@@ -10456,7 +10477,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="644" spans="1:5">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>149</v>
       </c>
@@ -10470,7 +10491,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="645" spans="1:5">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>283</v>
       </c>
@@ -10484,7 +10505,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="646" spans="1:5">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>192</v>
       </c>
@@ -10498,7 +10519,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="647" spans="1:5">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>284</v>
       </c>
@@ -10512,7 +10533,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="648" spans="1:5">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>238</v>
       </c>
@@ -10526,7 +10547,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="649" spans="1:5">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>177</v>
       </c>
@@ -10540,7 +10561,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="650" spans="1:5">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>285</v>
       </c>
@@ -10554,7 +10575,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="651" spans="1:5">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>279</v>
       </c>
@@ -10568,7 +10589,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="652" spans="1:5">
+    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>286</v>
       </c>
@@ -10582,7 +10603,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="653" spans="1:5">
+    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>287</v>
       </c>
@@ -10596,7 +10617,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="654" spans="1:5">
+    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>275</v>
       </c>
@@ -10610,7 +10631,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="655" spans="1:5">
+    <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>288</v>
       </c>
@@ -10624,7 +10645,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="656" spans="1:5">
+    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>244</v>
       </c>
@@ -10638,7 +10659,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="657" spans="1:5">
+    <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>245</v>
       </c>
@@ -10652,7 +10673,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="658" spans="1:5">
+    <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>244</v>
       </c>
@@ -10666,7 +10687,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="659" spans="1:5">
+    <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>244</v>
       </c>
@@ -10680,7 +10701,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="660" spans="1:5">
+    <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>200</v>
       </c>
@@ -10694,7 +10715,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="661" spans="1:5">
+    <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>289</v>
       </c>
@@ -10708,7 +10729,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="662" spans="1:5">
+    <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>164</v>
       </c>
@@ -10722,7 +10743,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="663" spans="1:5">
+    <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>185</v>
       </c>
@@ -10736,7 +10757,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="664" spans="1:5">
+    <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>121</v>
       </c>
@@ -10750,7 +10771,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="665" spans="1:5">
+    <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>252</v>
       </c>
@@ -10764,7 +10785,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="666" spans="1:5">
+    <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>204</v>
       </c>
@@ -10778,7 +10799,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="667" spans="1:5">
+    <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>164</v>
       </c>
@@ -10792,7 +10813,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="668" spans="1:5">
+    <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>290</v>
       </c>
@@ -10806,7 +10827,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="669" spans="1:5">
+    <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>273</v>
       </c>
@@ -10820,7 +10841,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="670" spans="1:5">
+    <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>291</v>
       </c>
@@ -10834,7 +10855,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="671" spans="1:5">
+    <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>208</v>
       </c>
@@ -10848,7 +10869,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="672" spans="1:5">
+    <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>291</v>
       </c>
@@ -10862,7 +10883,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="673" spans="1:5">
+    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>271</v>
       </c>
@@ -10876,7 +10897,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="674" spans="1:5">
+    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>271</v>
       </c>
@@ -10890,7 +10911,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="675" spans="1:5">
+    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>226</v>
       </c>
@@ -10904,7 +10925,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="676" spans="1:5">
+    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>240</v>
       </c>
@@ -10918,7 +10939,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="677" spans="1:5">
+    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>265</v>
       </c>
@@ -10932,7 +10953,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="678" spans="1:5">
+    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>255</v>
       </c>
@@ -10946,7 +10967,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="679" spans="1:5">
+    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>287</v>
       </c>
@@ -10960,7 +10981,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="680" spans="1:5">
+    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>280</v>
       </c>
@@ -10974,7 +10995,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="681" spans="1:5">
+    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>245</v>
       </c>
@@ -10988,7 +11009,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="682" spans="1:5">
+    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>245</v>
       </c>
@@ -11002,7 +11023,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="683" spans="1:5">
+    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>245</v>
       </c>
@@ -11016,7 +11037,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="684" spans="1:5">
+    <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>245</v>
       </c>
@@ -11030,7 +11051,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="685" spans="1:5">
+    <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>252</v>
       </c>
@@ -11044,7 +11065,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="686" spans="1:5">
+    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>155</v>
       </c>
@@ -11058,7 +11079,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="687" spans="1:5">
+    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>210</v>
       </c>
@@ -11072,7 +11093,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="688" spans="1:5">
+    <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>290</v>
       </c>
@@ -11086,7 +11107,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="689" spans="1:5">
+    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>190</v>
       </c>
@@ -11100,7 +11121,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="690" spans="1:5">
+    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>214</v>
       </c>
@@ -11114,7 +11135,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="691" spans="1:5">
+    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>210</v>
       </c>
@@ -11128,7 +11149,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="692" spans="1:5">
+    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>291</v>
       </c>
@@ -11142,7 +11163,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="693" spans="1:5">
+    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>291</v>
       </c>
@@ -11156,7 +11177,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="694" spans="1:5">
+    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>202</v>
       </c>
@@ -11170,7 +11191,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="695" spans="1:5">
+    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>221</v>
       </c>
@@ -11184,7 +11205,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="696" spans="1:5">
+    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>208</v>
       </c>
@@ -11198,7 +11219,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="697" spans="1:5">
+    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>215</v>
       </c>
@@ -11212,7 +11233,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="698" spans="1:5">
+    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>261</v>
       </c>
@@ -11226,7 +11247,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="699" spans="1:5">
+    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>221</v>
       </c>
@@ -11240,7 +11261,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="700" spans="1:5">
+    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>292</v>
       </c>
@@ -11254,7 +11275,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="701" spans="1:5">
+    <row r="701" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>280</v>
       </c>
@@ -11268,7 +11289,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="702" spans="1:5">
+    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>245</v>
       </c>
@@ -11282,7 +11303,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="703" spans="1:5">
+    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>287</v>
       </c>
@@ -11296,7 +11317,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="704" spans="1:5">
+    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>266</v>
       </c>
@@ -11310,7 +11331,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="705" spans="1:5">
+    <row r="705" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>293</v>
       </c>
@@ -11324,7 +11345,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="706" spans="1:5">
+    <row r="706" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>270</v>
       </c>
@@ -11338,7 +11359,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="707" spans="1:5">
+    <row r="707" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>192</v>
       </c>
@@ -11352,7 +11373,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="708" spans="1:5">
+    <row r="708" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>208</v>
       </c>
@@ -11366,7 +11387,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="709" spans="1:5">
+    <row r="709" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>222</v>
       </c>
@@ -11380,7 +11401,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="710" spans="1:5">
+    <row r="710" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>217</v>
       </c>
@@ -11394,7 +11415,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="711" spans="1:5">
+    <row r="711" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>294</v>
       </c>
@@ -11408,7 +11429,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="712" spans="1:5">
+    <row r="712" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>295</v>
       </c>
@@ -11422,7 +11443,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="713" spans="1:5">
+    <row r="713" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>294</v>
       </c>
@@ -11436,7 +11457,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="714" spans="1:5">
+    <row r="714" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>296</v>
       </c>
@@ -11450,7 +11471,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="715" spans="1:5">
+    <row r="715" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>277</v>
       </c>
@@ -11464,7 +11485,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="716" spans="1:5">
+    <row r="716" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>236</v>
       </c>
@@ -11478,7 +11499,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="717" spans="1:5">
+    <row r="717" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>284</v>
       </c>
@@ -11492,7 +11513,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="718" spans="1:5">
+    <row r="718" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>296</v>
       </c>
@@ -11506,7 +11527,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="719" spans="1:5">
+    <row r="719" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>241</v>
       </c>
@@ -11520,7 +11541,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="720" spans="1:5">
+    <row r="720" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>277</v>
       </c>
@@ -11534,7 +11555,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="721" spans="1:5">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>297</v>
       </c>
@@ -11548,7 +11569,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="722" spans="1:5">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>276</v>
       </c>
@@ -11562,7 +11583,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="723" spans="1:5">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>279</v>
       </c>
@@ -11576,7 +11597,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="724" spans="1:5">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>283</v>
       </c>
@@ -11590,7 +11611,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="725" spans="1:5">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>263</v>
       </c>
@@ -11604,7 +11625,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="726" spans="1:5">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>223</v>
       </c>
@@ -11618,7 +11639,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="727" spans="1:5">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>298</v>
       </c>
@@ -11632,7 +11653,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="728" spans="1:5">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>200</v>
       </c>
@@ -11646,7 +11667,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="729" spans="1:5">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>299</v>
       </c>
@@ -11660,7 +11681,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="730" spans="1:5">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>262</v>
       </c>
@@ -11674,7 +11695,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="731" spans="1:5">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>236</v>
       </c>
@@ -11688,7 +11709,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="732" spans="1:5">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>165</v>
       </c>
@@ -11702,7 +11723,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="733" spans="1:5">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>276</v>
       </c>
@@ -11716,7 +11737,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="734" spans="1:5">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>194</v>
       </c>
@@ -11730,7 +11751,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="735" spans="1:5">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>300</v>
       </c>
@@ -11744,7 +11765,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="736" spans="1:5">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>223</v>
       </c>
@@ -11758,7 +11779,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="737" spans="1:5">
+    <row r="737" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>226</v>
       </c>
@@ -11772,7 +11793,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="738" spans="1:5">
+    <row r="738" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>265</v>
       </c>
@@ -11786,7 +11807,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="739" spans="1:5">
+    <row r="739" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>293</v>
       </c>
@@ -11800,7 +11821,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="740" spans="1:5">
+    <row r="740" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>205</v>
       </c>
@@ -11814,7 +11835,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="741" spans="1:5">
+    <row r="741" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>273</v>
       </c>
@@ -11828,7 +11849,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="742" spans="1:5">
+    <row r="742" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>254</v>
       </c>
@@ -11842,7 +11863,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="743" spans="1:5">
+    <row r="743" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>296</v>
       </c>
@@ -11856,7 +11877,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="744" spans="1:5">
+    <row r="744" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>119</v>
       </c>
@@ -11870,7 +11891,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="745" spans="1:5">
+    <row r="745" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>239</v>
       </c>
@@ -11884,7 +11905,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="746" spans="1:5">
+    <row r="746" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>223</v>
       </c>
@@ -11898,7 +11919,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="747" spans="1:5">
+    <row r="747" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>239</v>
       </c>
@@ -11912,7 +11933,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="748" spans="1:5">
+    <row r="748" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>221</v>
       </c>
@@ -11926,7 +11947,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="749" spans="1:5">
+    <row r="749" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>245</v>
       </c>
@@ -11940,7 +11961,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="750" spans="1:5">
+    <row r="750" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>211</v>
       </c>
@@ -11954,7 +11975,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="751" spans="1:5">
+    <row r="751" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>245</v>
       </c>
@@ -11968,7 +11989,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="752" spans="1:5">
+    <row r="752" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>225</v>
       </c>
@@ -11982,7 +12003,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="753" spans="1:5">
+    <row r="753" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>301</v>
       </c>
@@ -11996,7 +12017,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="754" spans="1:5">
+    <row r="754" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>301</v>
       </c>
@@ -12010,7 +12031,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="755" spans="1:5">
+    <row r="755" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>243</v>
       </c>
@@ -12024,7 +12045,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="756" spans="1:5">
+    <row r="756" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>221</v>
       </c>
@@ -12038,7 +12059,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="757" spans="1:5">
+    <row r="757" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>221</v>
       </c>
@@ -12052,7 +12073,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="758" spans="1:5">
+    <row r="758" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>223</v>
       </c>
@@ -12066,7 +12087,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="759" spans="1:5">
+    <row r="759" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>177</v>
       </c>
@@ -12080,7 +12101,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="760" spans="1:5">
+    <row r="760" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>238</v>
       </c>
@@ -12094,7 +12115,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="761" spans="1:5">
+    <row r="761" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>204</v>
       </c>
@@ -12108,7 +12129,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="762" spans="1:5">
+    <row r="762" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>302</v>
       </c>
@@ -12122,7 +12143,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="763" spans="1:5">
+    <row r="763" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>225</v>
       </c>
@@ -12136,7 +12157,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="764" spans="1:5">
+    <row r="764" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>180</v>
       </c>
@@ -12150,7 +12171,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="765" spans="1:5">
+    <row r="765" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>241</v>
       </c>
@@ -12164,7 +12185,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="766" spans="1:5">
+    <row r="766" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>303</v>
       </c>
@@ -12178,7 +12199,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="767" spans="1:5">
+    <row r="767" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>304</v>
       </c>
@@ -12192,7 +12213,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="768" spans="1:5">
+    <row r="768" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>305</v>
       </c>
@@ -12206,7 +12227,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="769" spans="1:5">
+    <row r="769" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>254</v>
       </c>
@@ -12220,7 +12241,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="770" spans="1:5">
+    <row r="770" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>218</v>
       </c>
@@ -12234,7 +12255,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="771" spans="1:5">
+    <row r="771" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>226</v>
       </c>
@@ -12248,7 +12269,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="772" spans="1:5">
+    <row r="772" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>221</v>
       </c>
@@ -12262,7 +12283,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="773" spans="1:5">
+    <row r="773" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>155</v>
       </c>
@@ -12276,7 +12297,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="774" spans="1:5">
+    <row r="774" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>304</v>
       </c>
@@ -12290,7 +12311,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="775" spans="1:5">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>277</v>
       </c>
@@ -12304,7 +12325,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="776" spans="1:5">
+    <row r="776" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>278</v>
       </c>
@@ -12318,7 +12339,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="777" spans="1:5">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>275</v>
       </c>
@@ -12332,7 +12353,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="778" spans="1:5">
+    <row r="778" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>245</v>
       </c>
@@ -12346,7 +12367,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="779" spans="1:5">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>306</v>
       </c>
@@ -12360,7 +12381,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="780" spans="1:5">
+    <row r="780" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>180</v>
       </c>
@@ -12374,7 +12395,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="781" spans="1:5">
+    <row r="781" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>307</v>
       </c>
@@ -12388,7 +12409,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="782" spans="1:5">
+    <row r="782" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>288</v>
       </c>
@@ -12402,7 +12423,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="783" spans="1:5">
+    <row r="783" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>177</v>
       </c>
@@ -12416,7 +12437,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="784" spans="1:5">
+    <row r="784" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>176</v>
       </c>
@@ -12430,7 +12451,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="785" spans="1:5">
+    <row r="785" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>288</v>
       </c>
@@ -12444,7 +12465,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="786" spans="1:5">
+    <row r="786" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>280</v>
       </c>
@@ -12458,7 +12479,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="787" spans="1:5">
+    <row r="787" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>301</v>
       </c>
@@ -12472,7 +12493,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="788" spans="1:5">
+    <row r="788" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>257</v>
       </c>
@@ -12486,7 +12507,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="789" spans="1:5">
+    <row r="789" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>308</v>
       </c>
@@ -12500,7 +12521,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="790" spans="1:5">
+    <row r="790" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>274</v>
       </c>
@@ -12514,7 +12535,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="791" spans="1:5">
+    <row r="791" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>309</v>
       </c>
@@ -12528,7 +12549,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="792" spans="1:5">
+    <row r="792" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>276</v>
       </c>
@@ -12542,7 +12563,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="793" spans="1:5">
+    <row r="793" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>160</v>
       </c>
@@ -12556,7 +12577,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="794" spans="1:5">
+    <row r="794" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>245</v>
       </c>
@@ -12570,7 +12591,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="795" spans="1:5">
+    <row r="795" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>310</v>
       </c>
@@ -12584,7 +12605,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="796" spans="1:5">
+    <row r="796" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>311</v>
       </c>
@@ -12598,7 +12619,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="797" spans="1:5">
+    <row r="797" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>312</v>
       </c>
@@ -12612,7 +12633,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="798" spans="1:5">
+    <row r="798" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>245</v>
       </c>
@@ -12626,7 +12647,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="799" spans="1:5">
+    <row r="799" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>263</v>
       </c>
@@ -12640,7 +12661,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="800" spans="1:5">
+    <row r="800" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>242</v>
       </c>
@@ -12654,7 +12675,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="801" spans="1:5">
+    <row r="801" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>184</v>
       </c>
@@ -12668,7 +12689,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="802" spans="1:5">
+    <row r="802" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>288</v>
       </c>
@@ -12682,7 +12703,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="803" spans="1:5">
+    <row r="803" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>205</v>
       </c>
@@ -12696,7 +12717,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="804" spans="1:5">
+    <row r="804" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>245</v>
       </c>
@@ -12710,7 +12731,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="805" spans="1:5">
+    <row r="805" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>299</v>
       </c>
@@ -12724,7 +12745,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="806" spans="1:5">
+    <row r="806" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>194</v>
       </c>
@@ -12738,7 +12759,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="807" spans="1:5">
+    <row r="807" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>284</v>
       </c>
@@ -12752,7 +12773,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="808" spans="1:5">
+    <row r="808" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>255</v>
       </c>
@@ -12766,7 +12787,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="809" spans="1:5">
+    <row r="809" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>274</v>
       </c>
@@ -12780,7 +12801,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="810" spans="1:5">
+    <row r="810" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>312</v>
       </c>
@@ -12794,7 +12815,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="811" spans="1:5">
+    <row r="811" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>265</v>
       </c>
@@ -12808,7 +12829,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="812" spans="1:5">
+    <row r="812" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>306</v>
       </c>
@@ -12822,7 +12843,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="813" spans="1:5">
+    <row r="813" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>246</v>
       </c>
@@ -12836,7 +12857,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="814" spans="1:5">
+    <row r="814" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>245</v>
       </c>
@@ -12850,7 +12871,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="815" spans="1:5">
+    <row r="815" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A815" s="2">
         <v>45825</v>
       </c>
@@ -12864,7 +12885,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="816" spans="1:5">
+    <row r="816" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A816" s="2">
         <v>45864</v>
       </c>
@@ -12878,7 +12899,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="817" spans="1:5">
+    <row r="817" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A817" s="2">
         <v>45832</v>
       </c>
@@ -12892,7 +12913,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="818" spans="1:5">
+    <row r="818" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A818" s="2">
         <v>45820</v>
       </c>
@@ -12906,7 +12927,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="819" spans="1:5">
+    <row r="819" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A819" s="2">
         <v>45828</v>
       </c>
@@ -12920,7 +12941,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="820" spans="1:5">
+    <row r="820" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A820" s="2">
         <v>45837</v>
       </c>
@@ -12934,7 +12955,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="821" spans="1:5">
+    <row r="821" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A821" s="2">
         <v>45839</v>
       </c>
@@ -12948,7 +12969,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="822" spans="1:5">
+    <row r="822" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A822" s="2">
         <v>45825</v>
       </c>
@@ -12962,7 +12983,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="823" spans="1:5">
+    <row r="823" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A823" s="2">
         <v>45832</v>
       </c>
@@ -12976,7 +12997,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="824" spans="1:5">
+    <row r="824" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A824" s="2">
         <v>45839</v>
       </c>
@@ -12990,7 +13011,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="825" spans="1:5">
+    <row r="825" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A825" s="2">
         <v>45831</v>
       </c>
@@ -13004,7 +13025,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="826" spans="1:5">
+    <row r="826" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A826" s="2">
         <v>45820</v>
       </c>
@@ -13018,7 +13039,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="827" spans="1:5">
+    <row r="827" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A827" s="2">
         <v>45840</v>
       </c>
@@ -13032,7 +13053,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="828" spans="1:5">
+    <row r="828" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A828" s="2">
         <v>45826</v>
       </c>
@@ -13046,7 +13067,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="829" spans="1:5">
+    <row r="829" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A829" s="2">
         <v>45811</v>
       </c>
@@ -13060,7 +13081,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="830" spans="1:5">
+    <row r="830" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A830" s="2">
         <v>45830</v>
       </c>
@@ -13074,7 +13095,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="831" spans="1:5">
+    <row r="831" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A831" s="2">
         <v>45811</v>
       </c>
@@ -13088,7 +13109,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="832" spans="1:5">
+    <row r="832" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A832" s="2">
         <v>45835</v>
       </c>
@@ -13102,7 +13123,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="833" spans="1:5">
+    <row r="833" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A833" s="2">
         <v>45839</v>
       </c>
@@ -13116,7 +13137,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="834" spans="1:5">
+    <row r="834" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A834" s="3">
         <v>45836</v>
       </c>
@@ -13127,6 +13148,20 @@
         <v>80</v>
       </c>
       <c r="E834" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="835" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A835" s="3">
+        <v>45837</v>
+      </c>
+      <c r="B835" t="s">
+        <v>357</v>
+      </c>
+      <c r="C835">
+        <v>100</v>
+      </c>
+      <c r="E835" t="s">
         <v>356</v>
       </c>
     </row>

--- a/data/irrigation_records.xlsx
+++ b/data/irrigation_records.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="357">
   <si>
     <t>Date</t>
   </si>
@@ -1090,9 +1090,6 @@
   </si>
   <si>
     <t>2025/26</t>
-  </si>
-  <si>
-    <t>DG27004</t>
   </si>
 </sst>
 </file>
@@ -13156,7 +13153,7 @@
         <v>45837</v>
       </c>
       <c r="B835" t="s">
-        <v>357</v>
+        <v>313</v>
       </c>
       <c r="C835">
         <v>100</v>

--- a/data/irrigation_records.xlsx
+++ b/data/irrigation_records.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="364">
   <si>
     <t>Date</t>
   </si>
@@ -1484,7 +1484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1109"/>
+  <dimension ref="A1:I1191"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -12995,7 +12995,7 @@
         <v>45820</v>
       </c>
       <c r="B822" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C822">
         <v>100</v>
@@ -13009,7 +13009,7 @@
         <v>45820</v>
       </c>
       <c r="B823" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C823">
         <v>100</v>
@@ -13023,7 +13023,7 @@
         <v>45820</v>
       </c>
       <c r="B824" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="C824">
         <v>100</v>
@@ -13037,7 +13037,7 @@
         <v>45820</v>
       </c>
       <c r="B825" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C825">
         <v>100</v>
@@ -13051,7 +13051,7 @@
         <v>45820</v>
       </c>
       <c r="B826" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C826">
         <v>100</v>
@@ -13219,7 +13219,7 @@
         <v>45831</v>
       </c>
       <c r="B838" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C838">
         <v>100</v>
@@ -13233,7 +13233,7 @@
         <v>45831</v>
       </c>
       <c r="B839" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C839">
         <v>100</v>
@@ -16330,7 +16330,7 @@
         <v>45929</v>
       </c>
       <c r="B1060" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C1060">
         <v>100</v>
@@ -16341,10 +16341,10 @@
     </row>
     <row r="1061" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1061" s="2">
-        <v>45930</v>
+        <v>45929</v>
       </c>
       <c r="B1061" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="C1061">
         <v>100</v>
@@ -16358,7 +16358,7 @@
         <v>45930</v>
       </c>
       <c r="B1062" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="C1062">
         <v>100</v>
@@ -16369,10 +16369,10 @@
     </row>
     <row r="1063" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1063" s="2">
-        <v>45931</v>
+        <v>45930</v>
       </c>
       <c r="B1063" t="s">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="C1063">
         <v>100</v>
@@ -16386,7 +16386,7 @@
         <v>45931</v>
       </c>
       <c r="B1064" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="C1064">
         <v>100</v>
@@ -16400,7 +16400,7 @@
         <v>45931</v>
       </c>
       <c r="B1065" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="C1065">
         <v>100</v>
@@ -16414,7 +16414,7 @@
         <v>45931</v>
       </c>
       <c r="B1066" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C1066">
         <v>100</v>
@@ -16428,7 +16428,7 @@
         <v>45931</v>
       </c>
       <c r="B1067" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C1067">
         <v>100</v>
@@ -16442,7 +16442,7 @@
         <v>45931</v>
       </c>
       <c r="B1068" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C1068">
         <v>100</v>
@@ -16456,7 +16456,7 @@
         <v>45931</v>
       </c>
       <c r="B1069" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C1069">
         <v>100</v>
@@ -16467,10 +16467,10 @@
     </row>
     <row r="1070" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1070" s="2">
-        <v>45932</v>
+        <v>45931</v>
       </c>
       <c r="B1070" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="C1070">
         <v>100</v>
@@ -16484,7 +16484,7 @@
         <v>45932</v>
       </c>
       <c r="B1071" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="C1071">
         <v>100</v>
@@ -16498,7 +16498,7 @@
         <v>45932</v>
       </c>
       <c r="B1072" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C1072">
         <v>100</v>
@@ -16509,10 +16509,10 @@
     </row>
     <row r="1073" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1073" s="2">
-        <v>45933</v>
+        <v>45932</v>
       </c>
       <c r="B1073" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="C1073">
         <v>100</v>
@@ -16526,7 +16526,7 @@
         <v>45933</v>
       </c>
       <c r="B1074" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C1074">
         <v>100</v>
@@ -16540,7 +16540,7 @@
         <v>45933</v>
       </c>
       <c r="B1075" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C1075">
         <v>100</v>
@@ -16551,10 +16551,10 @@
     </row>
     <row r="1076" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1076" s="2">
-        <v>45934</v>
+        <v>45933</v>
       </c>
       <c r="B1076" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C1076">
         <v>100</v>
@@ -16568,7 +16568,7 @@
         <v>45934</v>
       </c>
       <c r="B1077" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="C1077">
         <v>100</v>
@@ -16579,10 +16579,10 @@
     </row>
     <row r="1078" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1078" s="2">
-        <v>45935</v>
+        <v>45934</v>
       </c>
       <c r="B1078" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="C1078">
         <v>100</v>
@@ -16596,7 +16596,7 @@
         <v>45935</v>
       </c>
       <c r="B1079" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="C1079">
         <v>100</v>
@@ -16607,10 +16607,10 @@
     </row>
     <row r="1080" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1080" s="2">
-        <v>45936</v>
+        <v>45935</v>
       </c>
       <c r="B1080" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="C1080">
         <v>100</v>
@@ -16624,7 +16624,7 @@
         <v>45936</v>
       </c>
       <c r="B1081" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C1081">
         <v>100</v>
@@ -16638,7 +16638,7 @@
         <v>45936</v>
       </c>
       <c r="B1082" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C1082">
         <v>100</v>
@@ -16652,7 +16652,7 @@
         <v>45936</v>
       </c>
       <c r="B1083" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C1083">
         <v>100</v>
@@ -16663,10 +16663,10 @@
     </row>
     <row r="1084" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1084" s="2">
-        <v>45937</v>
+        <v>45936</v>
       </c>
       <c r="B1084" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="C1084">
         <v>100</v>
@@ -16680,7 +16680,7 @@
         <v>45937</v>
       </c>
       <c r="B1085" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C1085">
         <v>100</v>
@@ -16694,7 +16694,7 @@
         <v>45937</v>
       </c>
       <c r="B1086" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="C1086">
         <v>100</v>
@@ -16705,10 +16705,10 @@
     </row>
     <row r="1087" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1087" s="2">
-        <v>45938</v>
+        <v>45937</v>
       </c>
       <c r="B1087" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="C1087">
         <v>100</v>
@@ -16722,7 +16722,7 @@
         <v>45938</v>
       </c>
       <c r="B1088" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="C1088">
         <v>100</v>
@@ -16736,7 +16736,7 @@
         <v>45938</v>
       </c>
       <c r="B1089" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="C1089">
         <v>100</v>
@@ -16747,10 +16747,10 @@
     </row>
     <row r="1090" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1090" s="2">
-        <v>45939</v>
+        <v>45938</v>
       </c>
       <c r="B1090" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="C1090">
         <v>100</v>
@@ -16764,7 +16764,7 @@
         <v>45939</v>
       </c>
       <c r="B1091" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C1091">
         <v>100</v>
@@ -16778,7 +16778,7 @@
         <v>45939</v>
       </c>
       <c r="B1092" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="C1092">
         <v>100</v>
@@ -16792,7 +16792,7 @@
         <v>45939</v>
       </c>
       <c r="B1093" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="C1093">
         <v>100</v>
@@ -16803,10 +16803,10 @@
     </row>
     <row r="1094" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1094" s="2">
-        <v>45940</v>
+        <v>45939</v>
       </c>
       <c r="B1094" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C1094">
         <v>100</v>
@@ -16820,7 +16820,7 @@
         <v>45940</v>
       </c>
       <c r="B1095" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="C1095">
         <v>100</v>
@@ -16834,7 +16834,7 @@
         <v>45940</v>
       </c>
       <c r="B1096" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C1096">
         <v>100</v>
@@ -16845,10 +16845,10 @@
     </row>
     <row r="1097" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1097" s="2">
-        <v>45941</v>
+        <v>45940</v>
       </c>
       <c r="B1097" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="C1097">
         <v>100</v>
@@ -16859,10 +16859,10 @@
     </row>
     <row r="1098" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1098" s="2">
-        <v>45942</v>
+        <v>45941</v>
       </c>
       <c r="B1098" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C1098">
         <v>100</v>
@@ -16873,10 +16873,10 @@
     </row>
     <row r="1099" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1099" s="2">
-        <v>45942</v>
+        <v>45941</v>
       </c>
       <c r="B1099" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C1099">
         <v>100</v>
@@ -16890,7 +16890,7 @@
         <v>45942</v>
       </c>
       <c r="B1100" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="C1100">
         <v>100</v>
@@ -16904,7 +16904,7 @@
         <v>45942</v>
       </c>
       <c r="B1101" t="s">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="C1101">
         <v>100</v>
@@ -16918,7 +16918,7 @@
         <v>45942</v>
       </c>
       <c r="B1102" t="s">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="C1102">
         <v>100</v>
@@ -16932,7 +16932,7 @@
         <v>45942</v>
       </c>
       <c r="B1103" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C1103">
         <v>100</v>
@@ -16943,10 +16943,10 @@
     </row>
     <row r="1104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1104" s="2">
-        <v>45943</v>
+        <v>45942</v>
       </c>
       <c r="B1104" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="C1104">
         <v>100</v>
@@ -16957,10 +16957,10 @@
     </row>
     <row r="1105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1105" s="2">
-        <v>45943</v>
+        <v>45942</v>
       </c>
       <c r="B1105" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C1105">
         <v>100</v>
@@ -16971,10 +16971,10 @@
     </row>
     <row r="1106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1106" s="2">
-        <v>45944</v>
+        <v>45943</v>
       </c>
       <c r="B1106" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C1106">
         <v>100</v>
@@ -16985,10 +16985,10 @@
     </row>
     <row r="1107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1107" s="2">
-        <v>45946</v>
+        <v>45943</v>
       </c>
       <c r="B1107" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="C1107">
         <v>100</v>
@@ -16999,10 +16999,10 @@
     </row>
     <row r="1108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1108" s="2">
-        <v>45947</v>
+        <v>45944</v>
       </c>
       <c r="B1108" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C1108">
         <v>100</v>
@@ -17013,16 +17013,660 @@
     </row>
     <row r="1109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1109" s="2">
+        <v>45946</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1109">
+        <v>100</v>
+      </c>
+      <c r="E1109" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1110" s="2">
+        <v>45946</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1110">
+        <v>100</v>
+      </c>
+      <c r="E1110" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1111" s="2">
         <v>45947</v>
       </c>
-      <c r="B1109" t="s">
+      <c r="B1111" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1111">
+        <v>100</v>
+      </c>
+      <c r="E1111" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1112" s="2">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1113" s="2">
+        <v>45948</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1114" s="2">
+        <v>45949</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1115" s="2">
+        <v>45950</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>351</v>
+      </c>
+      <c r="C1115">
+        <v>100</v>
+      </c>
+      <c r="E1115" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1116" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1116">
+        <v>100</v>
+      </c>
+      <c r="E1116" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1117" s="2">
+        <v>45952</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1117">
+        <v>100</v>
+      </c>
+      <c r="E1117" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1118" s="2">
+        <v>45952</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1118">
+        <v>100</v>
+      </c>
+      <c r="E1118" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1119" s="2">
+        <v>45953</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1119">
+        <v>100</v>
+      </c>
+      <c r="E1119" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1120" s="2">
+        <v>45953</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1120">
+        <v>100</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1121" s="2">
+        <v>45953</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>343</v>
+      </c>
+      <c r="C1121">
+        <v>100</v>
+      </c>
+      <c r="E1121" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1122" s="2">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1123" s="2">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1124" s="2">
+        <v>45956</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1125" s="2">
+        <v>45957</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1125">
+        <v>100</v>
+      </c>
+      <c r="E1125" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1126" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>358</v>
+      </c>
+      <c r="C1126">
+        <v>100</v>
+      </c>
+      <c r="E1126" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1127" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>331</v>
+      </c>
+      <c r="C1127">
+        <v>100</v>
+      </c>
+      <c r="E1127" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1128" s="2">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1129" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1129">
+        <v>100</v>
+      </c>
+      <c r="E1129" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1130" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1131" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1131">
+        <v>100</v>
+      </c>
+      <c r="E1131" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1132" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B1132" t="s">
         <v>335</v>
       </c>
-      <c r="C1109">
-        <v>100</v>
-      </c>
-      <c r="E1109" t="s">
-        <v>363</v>
+      <c r="C1132">
+        <v>100</v>
+      </c>
+      <c r="E1132" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1133" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1133">
+        <v>100</v>
+      </c>
+      <c r="E1133" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1134" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1134">
+        <v>100</v>
+      </c>
+      <c r="E1134" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1135" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1135">
+        <v>100</v>
+      </c>
+      <c r="E1135" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1136" s="2">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1137" s="2">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1138" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1138">
+        <v>100</v>
+      </c>
+      <c r="E1138" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1139" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1140" s="2">
+        <v>45970</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1141" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1141">
+        <v>100</v>
+      </c>
+      <c r="E1141" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1142" s="2">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1143" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1143">
+        <v>100</v>
+      </c>
+      <c r="E1143" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1144" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1144">
+        <v>100</v>
+      </c>
+      <c r="E1144" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1145" s="2">
+        <v>45975</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1146" s="2">
+        <v>45976</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1147" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1148" s="2">
+        <v>45978</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1149" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1149">
+        <v>100</v>
+      </c>
+      <c r="E1149" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1150" s="2">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1151" s="2">
+        <v>45981</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1152" s="2">
+        <v>45982</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1153" s="2">
+        <v>45983</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1154" s="2">
+        <v>45984</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1155" s="2">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1156" s="2">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1157" s="2">
+        <v>45987</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>349</v>
+      </c>
+      <c r="C1157">
+        <v>100</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1158" s="2">
+        <v>45988</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1158">
+        <v>100</v>
+      </c>
+      <c r="E1158" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1159" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1159">
+        <v>100</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1160" s="2">
+        <v>45990</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1161" s="2">
+        <v>45991</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1162" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1163" s="2">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1164" s="2">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1165" s="2">
+        <v>45995</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1166" s="2">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1167" s="2">
+        <v>45997</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1168" s="2">
+        <v>45998</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1169" s="2">
+        <v>45999</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1170" s="2">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1171" s="2">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1172" s="2">
+        <v>46002</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1173" s="2">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1174" s="2">
+        <v>46004</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1175" s="2">
+        <v>46005</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1176" s="2">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1177" s="2">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1178" s="2">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1179" s="2">
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1180" s="2">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1181" s="2">
+        <v>46011</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1182" s="2">
+        <v>46012</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1183" s="2">
+        <v>46013</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1184" s="2">
+        <v>46014</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1185" s="2">
+        <v>46015</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1186" s="2">
+        <v>46016</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1187" s="2">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1188" s="2">
+        <v>46018</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1189" s="2">
+        <v>46019</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1190" s="2">
+        <v>46020</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1191" s="2">
+        <v>46021</v>
       </c>
     </row>
   </sheetData>
